--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080" activeTab="2"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="182">
   <si>
     <t>##var</t>
   </si>
@@ -76,7 +76,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>全名</t>
@@ -94,7 +94,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>包含模块和名字</t>
@@ -114,7 +114,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>是否为位标记枚举</t>
@@ -125,7 +125,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>枚举项是否唯一</t>
@@ -136,7 +136,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>注释</t>
@@ -147,7 +147,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>枚举级标签</t>
@@ -158,7 +158,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>枚举名</t>
@@ -169,7 +169,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>别名</t>
@@ -180,7 +180,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>值</t>
@@ -191,7 +191,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>枚举项标签</t>
@@ -208,7 +208,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>稀有度</t>
@@ -225,7 +225,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>无</t>
@@ -239,7 +239,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>白</t>
@@ -253,7 +253,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>绿</t>
@@ -267,7 +267,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>蓝</t>
@@ -281,7 +281,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>金</t>
@@ -295,7 +295,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>红</t>
@@ -309,7 +309,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物品类型</t>
@@ -323,7 +323,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>战利品</t>
@@ -337,7 +337,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>装备</t>
@@ -351,7 +351,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>消耗品</t>
@@ -365,7 +365,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>装备栏类型</t>
@@ -379,7 +379,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>武器</t>
@@ -393,7 +393,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>防具</t>
@@ -407,7 +407,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>难度档位</t>
@@ -421,7 +421,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>难度</t>
@@ -444,7 +444,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>难度</t>
@@ -467,7 +467,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>难度</t>
@@ -490,7 +490,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>战斗属性类型</t>
@@ -504,7 +504,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>当前生命</t>
@@ -518,7 +518,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>当前魔力</t>
@@ -532,7 +532,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>生命上限</t>
@@ -546,7 +546,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>魔力上限</t>
@@ -560,7 +560,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>攻击力</t>
@@ -574,7 +574,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>魔力</t>
@@ -588,21 +588,21 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>速度</t>
     </r>
   </si>
   <si>
-    <t>RunResultType</t>
+    <t>RoundResultType</t>
   </si>
   <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单局结算类型</t>
@@ -616,7 +616,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>成功撤离</t>
@@ -630,7 +630,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>全员阵亡</t>
@@ -644,7 +644,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>超时失败</t>
@@ -658,7 +658,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>主动退出</t>
@@ -671,7 +671,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>场景类型</t>
@@ -684,7 +684,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>启动场景</t>
@@ -697,7 +697,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>菜单场景</t>
@@ -710,7 +710,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>主场景</t>
@@ -723,7 +723,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人队伍威胁等级</t>
@@ -733,7 +733,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>无</t>
@@ -746,7 +746,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>低</t>
@@ -759,7 +759,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>中</t>
@@ -772,7 +772,7 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>高</t>
@@ -1020,84 +1020,87 @@
     <t>随机行动</t>
   </si>
   <si>
-    <r>
-      <t>全名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
+    <t>UIFormType</t>
+  </si>
+  <si>
+    <t>界面类型</t>
+  </si>
+  <si>
+    <t>Undefined</t>
+  </si>
+  <si>
+    <t>未定义</t>
+  </si>
+  <si>
+    <t>DialogForm</t>
+  </si>
+  <si>
+    <t>弹出框</t>
+  </si>
+  <si>
+    <t>LobbyForm</t>
+  </si>
+  <si>
+    <t>大厅界面</t>
+  </si>
+  <si>
+    <t>SettingForm</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>AboutForm</t>
+  </si>
+  <si>
+    <t>关于</t>
+  </si>
+  <si>
+    <t>BattleForm</t>
+  </si>
+  <si>
+    <t>战斗界面</t>
+  </si>
+  <si>
+    <t>JoystickForm</t>
+  </si>
+  <si>
+    <t>输入面板</t>
+  </si>
+  <si>
+    <t>RoundHUDForm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>包含模块和名字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Consolas"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>UIFormType</t>
-  </si>
-  <si>
-    <t>界面类型</t>
-  </si>
-  <si>
-    <t>Undefined</t>
-  </si>
-  <si>
-    <t>未定义</t>
-  </si>
-  <si>
-    <t>DialogForm</t>
-  </si>
-  <si>
-    <t>弹出框</t>
-  </si>
-  <si>
-    <t>LobbyForm</t>
-  </si>
-  <si>
-    <t>大厅界面</t>
-  </si>
-  <si>
-    <t>SettingForm</t>
-  </si>
-  <si>
-    <t>设置</t>
-  </si>
-  <si>
-    <t>AboutForm</t>
-  </si>
-  <si>
-    <t>关于</t>
-  </si>
-  <si>
-    <t>BattleForm</t>
-  </si>
-  <si>
-    <t>战斗界面</t>
-  </si>
-  <si>
-    <t>JoystickForm</t>
-  </si>
-  <si>
-    <t>输入面板</t>
+      <t>HUD</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>面板</t>
+    </r>
+  </si>
+  <si>
+    <t>RoundBackpackForm</t>
+  </si>
+  <si>
+    <t>局内背包面板</t>
   </si>
 </sst>
 </file>
@@ -1136,12 +1139,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1326,7 +1329,7 @@
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="宋体"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -2369,11 +2372,11 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.75" style="1" customWidth="1"/>
     <col min="3" max="3" width="19.35" style="1" customWidth="1"/>
     <col min="4" max="4" width="15.925" style="1" customWidth="1"/>
     <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="6" width="15.4416666666667" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5833333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="26.7166666666667" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.075" style="1" customWidth="1"/>
     <col min="9" max="12" width="10" style="1" customWidth="1"/>
@@ -4023,7 +4026,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.94166666666667" style="1"/>
@@ -4033,11 +4036,12 @@
     <col min="5" max="5" width="10.4083333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="10.9083333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.1583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1666666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.6666666666667" style="1" customWidth="1"/>
     <col min="9" max="9" width="12.7416666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.6416666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.5916666666667" style="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.94166666666667" style="1"/>
+    <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.94166666666667" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -4101,7 +4105,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>162</v>
+        <v>12</v>
       </c>
       <c r="C3" s="9" t="s">
         <v>103</v>
@@ -4134,7 +4138,7 @@
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>0</v>
@@ -4146,16 +4150,16 @@
         <v>22</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>165</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>166</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -4166,10 +4170,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" s="11" t="s">
         <v>167</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>168</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -4180,10 +4184,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>169</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>170</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
@@ -4194,10 +4198,10 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>171</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>172</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
@@ -4208,10 +4212,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>173</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>174</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
@@ -4222,10 +4226,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>176</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>
@@ -4233,13 +4237,35 @@
     </row>
     <row r="11" customHeight="1" spans="1:12">
       <c r="H11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>177</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>178</v>
       </c>
       <c r="J11" s="1">
         <v>104</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="H12" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="J12" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="H13" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="J13" s="1">
+        <v>106</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView windowWidth="24750" windowHeight="12080" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Normal" sheetId="1" r:id="rId1"/>
-    <sheet name="Battle" sheetId="2" r:id="rId2"/>
-    <sheet name="UI" sheetId="3" r:id="rId3"/>
+    <sheet name="Exploration" sheetId="4" r:id="rId2"/>
+    <sheet name="Battle" sheetId="2" r:id="rId3"/>
+    <sheet name="UI" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="188">
   <si>
     <t>##var</t>
   </si>
@@ -595,6 +596,58 @@
     </r>
   </si>
   <si>
+    <t>SceneType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>场景类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Launch</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>启动场景</t>
+    </r>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜单场景</t>
+    </r>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主场景</t>
+    </r>
+  </si>
+  <si>
     <t>RoundResultType</t>
   </si>
   <si>
@@ -665,58 +718,6 @@
     </r>
   </si>
   <si>
-    <t>SceneType</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>场景类型</t>
-    </r>
-  </si>
-  <si>
-    <t>Launch</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>启动场景</t>
-    </r>
-  </si>
-  <si>
-    <t>Menu</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>菜单场景</t>
-    </r>
-  </si>
-  <si>
-    <t>Main</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微软雅黑"/>
-        <charset val="134"/>
-      </rPr>
-      <t>主场景</t>
-    </r>
-  </si>
-  <si>
     <t>EnemyPartyThreatLevel</t>
   </si>
   <si>
@@ -779,207 +780,424 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>全名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>包含模块和名字</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>是否为位标记枚举</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>枚举级标签</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>枚举项标签</t>
+    <t>RoomType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>房间类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>普通房间</t>
+    </r>
+  </si>
+  <si>
+    <t>Corridor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>走廊</t>
+    </r>
+  </si>
+  <si>
+    <t>EnemyExplorationState</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人巡逻状态</t>
+    </r>
+  </si>
+  <si>
+    <t>Patrol</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>巡逻</t>
+    </r>
+  </si>
+  <si>
+    <t>Pursuit</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>追击</t>
+    </r>
+  </si>
+  <si>
+    <t>LostTarget</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>丢失目标</t>
+    </r>
   </si>
   <si>
     <t>BattleActionType</t>
   </si>
   <si>
-    <t>战斗行动类型</t>
-  </si>
-  <si>
-    <t>无</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗行动类型</t>
+    </r>
   </si>
   <si>
     <t>Attack</t>
   </si>
   <si>
-    <t>攻击</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>攻击</t>
+    </r>
   </si>
   <si>
     <t>Skill</t>
   </si>
   <si>
-    <t>技能</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>技能</t>
+    </r>
   </si>
   <si>
     <t>Item</t>
   </si>
   <si>
-    <t>道具</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>道具</t>
+    </r>
   </si>
   <si>
     <t>Escape</t>
   </si>
   <si>
-    <t>逃跑</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>逃跑</t>
+    </r>
   </si>
   <si>
     <t>BattleTargetType</t>
   </si>
   <si>
-    <t>战斗目标类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗目标类型</t>
+    </r>
   </si>
   <si>
     <t>Self</t>
   </si>
   <si>
-    <t>自己</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自己</t>
+    </r>
   </si>
   <si>
     <t>SingleAlly</t>
   </si>
   <si>
-    <t>单个友方</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单个友方</t>
+    </r>
   </si>
   <si>
     <t>AllAllies</t>
   </si>
   <si>
-    <t>全体友方</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全体友方</t>
+    </r>
   </si>
   <si>
     <t>SingleEnemy</t>
   </si>
   <si>
-    <t>单个敌方</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单个敌方</t>
+    </r>
   </si>
   <si>
     <t>AllEnemies</t>
   </si>
   <si>
-    <t>全体敌方</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全体敌方</t>
+    </r>
   </si>
   <si>
     <t>BattleStateType</t>
   </si>
   <si>
-    <t>战斗状态类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗状态类型</t>
+    </r>
   </si>
   <si>
     <t>Stun</t>
   </si>
   <si>
-    <t>眩晕</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>眩晕</t>
+    </r>
   </si>
   <si>
     <t>BattleOutcomeType</t>
   </si>
   <si>
-    <t>战斗结果类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗结果类型</t>
+    </r>
   </si>
   <si>
     <t>Victory</t>
   </si>
   <si>
-    <t>胜利</t>
-  </si>
-  <si>
-    <t>所有敌人阵亡。</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>胜利</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所有敌人阵亡。</t>
+    </r>
   </si>
   <si>
     <t>AllEscaped</t>
   </si>
   <si>
-    <t>全部逃脱</t>
-  </si>
-  <si>
-    <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全部逃脱</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所有玩家成功逃跑，且没有玩家阵亡。</t>
+    </r>
   </si>
   <si>
     <t>PartialEscapeDefeat</t>
   </si>
   <si>
-    <t>部分逃脱失败</t>
-  </si>
-  <si>
-    <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部分逃脱失败</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>至少一名玩家逃跑，其余仍在战斗中的玩家全部阵亡。</t>
+    </r>
   </si>
   <si>
     <t>TotalDefeat</t>
   </si>
   <si>
-    <t>全部失败</t>
-  </si>
-  <si>
-    <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全部失败</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>所有玩家阵亡，没有任何玩家成功逃跑。</t>
+    </r>
   </si>
   <si>
     <t>BattleFactionType</t>
   </si>
   <si>
-    <t>回合制阵营类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>回合制阵营类型</t>
+    </r>
   </si>
   <si>
     <t>Player</t>
   </si>
   <si>
-    <t>玩家</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>玩家</t>
+    </r>
   </si>
   <si>
     <t>Enemy</t>
   </si>
   <si>
-    <t>敌人</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>敌人</t>
+    </r>
   </si>
   <si>
     <t>EnemyAiType</t>
@@ -989,7 +1207,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>敌人</t>
@@ -998,7 +1216,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>AI</t>
@@ -1007,7 +1225,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>类型</t>
@@ -1017,55 +1235,119 @@
     <t>Random</t>
   </si>
   <si>
-    <t>随机行动</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>随机行动</t>
+    </r>
   </si>
   <si>
     <t>UIFormType</t>
   </si>
   <si>
-    <t>界面类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>界面类型</t>
+    </r>
   </si>
   <si>
     <t>Undefined</t>
   </si>
   <si>
-    <t>未定义</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未定义</t>
+    </r>
   </si>
   <si>
     <t>DialogForm</t>
   </si>
   <si>
-    <t>弹出框</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>弹出框</t>
+    </r>
   </si>
   <si>
     <t>LobbyForm</t>
   </si>
   <si>
-    <t>大厅界面</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大厅界面</t>
+    </r>
   </si>
   <si>
     <t>SettingForm</t>
   </si>
   <si>
-    <t>设置</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>设置</t>
+    </r>
   </si>
   <si>
     <t>AboutForm</t>
   </si>
   <si>
-    <t>关于</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>关于</t>
+    </r>
   </si>
   <si>
     <t>BattleForm</t>
   </si>
   <si>
-    <t>战斗界面</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战斗界面</t>
+    </r>
   </si>
   <si>
     <t>JoystickForm</t>
   </si>
   <si>
-    <t>输入面板</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>输入面板</t>
+    </r>
   </si>
   <si>
     <t>RoundHUDForm</t>
@@ -1100,7 +1382,27 @@
     <t>RoundBackpackForm</t>
   </si>
   <si>
-    <t>局内背包面板</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内背包面板</t>
+    </r>
+  </si>
+  <si>
+    <t>RoundSettlementForm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>局内结算面板</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1113,7 +1415,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1138,68 +1440,12 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="宋体-简"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Consolas"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
       <name val="Consolas"/>
       <charset val="134"/>
     </font>
@@ -1328,7 +1574,18 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1683,153 +1940,153 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="16" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -1850,51 +2107,24 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2368,7 +2598,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -2476,944 +2706,829 @@
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:12">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
     </row>
     <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="25" t="b">
+      <c r="C5" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="25" t="b">
+      <c r="D5" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="25" t="s">
+      <c r="I5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="10">
         <v>0</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
     </row>
     <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25" t="s">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="10">
         <v>1</v>
       </c>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="25"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25" t="s">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="10">
         <v>2</v>
       </c>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
     </row>
     <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25" t="s">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="I8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="10">
         <v>3</v>
       </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25" t="s">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="10">
         <v>4</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25" t="s">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="10">
         <v>5</v>
       </c>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="25"/>
-      <c r="B12" s="25" t="s">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="25" t="b">
+      <c r="C12" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D12" s="25" t="b">
+      <c r="D12" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="10">
         <v>0</v>
       </c>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="25"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25" t="s">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="10">
         <v>1</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="25"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25" t="s">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="10">
         <v>2</v>
       </c>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25" t="s">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="10">
         <v>3</v>
       </c>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
     </row>
     <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
     </row>
     <row r="17" customHeight="1" spans="1:12">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25" t="s">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="25" t="b">
+      <c r="C17" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D17" s="25" t="b">
+      <c r="D17" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="25" t="s">
+      <c r="H17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="25" t="s">
+      <c r="I17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="10">
         <v>0</v>
       </c>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
     </row>
     <row r="18" customHeight="1" spans="1:12">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25" t="s">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="I18" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="10">
         <v>1</v>
       </c>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
     </row>
     <row r="19" customHeight="1" spans="1:12">
-      <c r="A19" s="25"/>
-      <c r="B19" s="25"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25" t="s">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="I19" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="10">
         <v>2</v>
       </c>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
     </row>
     <row r="20" customHeight="1" spans="1:12">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
     </row>
     <row r="21" customHeight="1" spans="1:12">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25" t="s">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="25" t="b">
+      <c r="C21" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D21" s="25" t="b">
+      <c r="D21" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="25" t="s">
+      <c r="H21" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I21" s="25" t="s">
+      <c r="I21" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="10">
         <v>0</v>
       </c>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
     </row>
     <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25" t="s">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I22" s="25" t="s">
+      <c r="I22" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="10">
         <v>1</v>
       </c>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
     </row>
     <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="25"/>
-      <c r="B23" s="25"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25" t="s">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="I23" s="25" t="s">
+      <c r="I23" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="10">
         <v>2</v>
       </c>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
     </row>
     <row r="24" customHeight="1" spans="1:12">
-      <c r="A24" s="25"/>
-      <c r="B24" s="25"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25" t="s">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="I24" s="25" t="s">
+      <c r="I24" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="10">
         <v>3</v>
       </c>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-    </row>
-    <row r="25" s="24" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="26"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="26"/>
-      <c r="J25" s="26"/>
-      <c r="K25" s="26"/>
-      <c r="L25" s="26"/>
-    </row>
-    <row r="26" s="24" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="26"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26"/>
-      <c r="G26" s="26"/>
-      <c r="H26" s="26"/>
-      <c r="I26" s="26"/>
-      <c r="J26" s="26"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="26"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" s="13" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+    </row>
+    <row r="26" s="13" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="14"/>
+      <c r="B26" s="14"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
     </row>
     <row r="27" customHeight="1" spans="1:12">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="10"/>
+      <c r="L27" s="10"/>
     </row>
     <row r="28" customHeight="1" spans="1:12">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25" t="s">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C28" s="25" t="b">
+      <c r="C28" s="10" t="b">
         <v>0</v>
       </c>
-      <c r="D28" s="25" t="b">
+      <c r="D28" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="E28" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F28" s="25" t="s">
+      <c r="F28" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H28" s="25" t="s">
+      <c r="H28" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="25" t="s">
+      <c r="I28" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="10">
         <v>0</v>
       </c>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
     </row>
     <row r="29" customHeight="1" spans="1:12">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25" t="s">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="I29" s="25" t="s">
+      <c r="I29" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="10">
         <v>1</v>
       </c>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
+      <c r="K29" s="10"/>
+      <c r="L29" s="10"/>
     </row>
     <row r="30" customHeight="1" spans="1:12">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25" t="s">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="I30" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="10">
         <v>2</v>
       </c>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
+      <c r="K30" s="10"/>
+      <c r="L30" s="10"/>
     </row>
     <row r="31" customHeight="1" spans="1:12">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25" t="s">
+      <c r="A31" s="10"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="25" t="s">
+      <c r="I31" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="10">
         <v>3</v>
       </c>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" customHeight="1" spans="1:12">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25" t="s">
+      <c r="A32" s="10"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="I32" s="25" t="s">
+      <c r="I32" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="10">
         <v>4</v>
       </c>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
+      <c r="K32" s="10"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" customHeight="1" spans="1:12">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25" t="s">
+      <c r="A33" s="10"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I33" s="25" t="s">
+      <c r="I33" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="10">
         <v>5</v>
       </c>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
+      <c r="K33" s="10"/>
+      <c r="L33" s="10"/>
     </row>
     <row r="34" customHeight="1" spans="1:12">
-      <c r="A34" s="25"/>
-      <c r="B34" s="25"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25" t="s">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I34" s="25" t="s">
+      <c r="I34" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="10">
         <v>6</v>
       </c>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
     </row>
     <row r="35" customHeight="1" spans="1:12">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25" t="s">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I35" s="25" t="s">
+      <c r="I35" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="10">
         <v>7</v>
       </c>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
     </row>
     <row r="36" customHeight="1" spans="1:12">
-      <c r="A36" s="25"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="25"/>
-      <c r="L36" s="25"/>
-    </row>
-    <row r="37" s="24" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26"/>
-      <c r="G37" s="26"/>
-      <c r="H37" s="26"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
+      <c r="A36" s="10"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+      <c r="I36" s="10"/>
+      <c r="J36" s="10"/>
+      <c r="K36" s="10"/>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" s="13" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
     </row>
     <row r="38" customHeight="1" spans="1:12">
-      <c r="A38" s="25"/>
-      <c r="B38" s="25"/>
-      <c r="C38" s="25"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="25"/>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="25"/>
-      <c r="L38" s="25"/>
-    </row>
-    <row r="39" customHeight="1" spans="1:12">
-      <c r="A39" s="25"/>
-      <c r="B39" s="25" t="s">
+      <c r="A38" s="10"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+    </row>
+    <row r="40" customHeight="1" spans="1:12">
+      <c r="B40" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C39" s="25" t="b">
+      <c r="C40" s="1">
         <v>0</v>
       </c>
-      <c r="D39" s="25" t="b">
+      <c r="D40" s="1">
         <v>1</v>
       </c>
-      <c r="E39" s="25" t="s">
+      <c r="E40" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F39" s="25" t="s">
+      <c r="F40" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G39" s="25" t="s">
+      <c r="G40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="I39" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="J39" s="25">
+      <c r="H40" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J40" s="1">
         <v>0</v>
       </c>
-      <c r="K39" s="25"/>
-      <c r="L39" s="25"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
-      <c r="A40" s="25"/>
-      <c r="B40" s="25"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="25"/>
-      <c r="G40" s="25"/>
-      <c r="H40" s="25" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="J40" s="25">
+    </row>
+    <row r="41" customHeight="1" spans="1:12">
+      <c r="H41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="1">
         <v>1</v>
       </c>
-      <c r="K40" s="25"/>
-      <c r="L40" s="25"/>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="25"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="25"/>
-      <c r="H41" s="25" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="25" t="s">
-        <v>80</v>
-      </c>
-      <c r="J41" s="25">
+    </row>
+    <row r="42" customHeight="1" spans="1:12">
+      <c r="H42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J42" s="1">
         <v>2</v>
       </c>
-      <c r="K41" s="25"/>
-      <c r="L41" s="25"/>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
-      <c r="F42" s="25"/>
-      <c r="G42" s="25"/>
-      <c r="H42" s="25" t="s">
-        <v>81</v>
-      </c>
-      <c r="I42" s="25" t="s">
-        <v>82</v>
-      </c>
-      <c r="J42" s="25">
-        <v>3</v>
-      </c>
-      <c r="K42" s="25"/>
-      <c r="L42" s="25"/>
-    </row>
-    <row r="43" customHeight="1" spans="1:12">
-      <c r="A43" s="25"/>
-      <c r="B43" s="25"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="25"/>
-      <c r="E43" s="25"/>
-      <c r="F43" s="25"/>
-      <c r="G43" s="25"/>
-      <c r="H43" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="I43" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="J43" s="25">
-        <v>4</v>
-      </c>
-      <c r="K43" s="25"/>
-      <c r="L43" s="25"/>
-    </row>
-    <row r="44" customHeight="1" spans="1:12">
-      <c r="A44" s="25"/>
-      <c r="B44" s="25"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="25"/>
-      <c r="E44" s="25"/>
-      <c r="F44" s="25"/>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-    </row>
-    <row r="46" customHeight="1" spans="1:12">
-      <c r="B46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C46" s="1">
-        <v>0</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="1:12">
-      <c r="H47" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J47" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" customHeight="1" spans="1:12">
-      <c r="H48" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J48" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" customHeight="1" spans="2:10">
-      <c r="B51" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="D51" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="2:10">
-      <c r="H52" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J52" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="2:10">
-      <c r="H53" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I53" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J53" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="2:10">
-      <c r="H54" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I54" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J54" s="1">
-        <v>3</v>
-      </c>
-    </row>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
+      <c r="K45" s="15"/>
+      <c r="L45" s="15"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="15"/>
+      <c r="J46" s="15"/>
+      <c r="K46" s="15"/>
+      <c r="L46" s="15"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="15"/>
+      <c r="J47" s="15"/>
+      <c r="K47" s="15"/>
+      <c r="L47" s="15"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="15"/>
+      <c r="E48" s="15"/>
+      <c r="F48" s="15"/>
+      <c r="G48" s="15"/>
+      <c r="H48" s="15"/>
+      <c r="I48" s="15"/>
+      <c r="J48" s="15"/>
+      <c r="K48" s="15"/>
+      <c r="L48" s="15"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="15"/>
+      <c r="E49" s="15"/>
+      <c r="F49" s="15"/>
+      <c r="G49" s="15"/>
+      <c r="H49" s="15"/>
+      <c r="I49" s="15"/>
+      <c r="J49" s="15"/>
+      <c r="K49" s="15"/>
+      <c r="L49" s="15"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1"/>
+    <row r="52" customFormat="1" customHeight="1"/>
+    <row r="53" customFormat="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
@@ -3426,593 +3541,382 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L35"/>
-  <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
+  <dimension ref="A1:L22"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.94166666666667" style="12"/>
-    <col min="2" max="2" width="21.5666666666667" style="12" customWidth="1"/>
-    <col min="3" max="3" width="17.525" style="12" customWidth="1"/>
-    <col min="4" max="4" width="17.4083333333333" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8.94166666666667" style="12"/>
-    <col min="6" max="6" width="15.075" style="12" customWidth="1"/>
-    <col min="7" max="7" width="23.2833333333333" style="12" customWidth="1"/>
-    <col min="8" max="8" width="23.0333333333333" style="12" customWidth="1"/>
-    <col min="9" max="9" width="11.6416666666667" style="12" customWidth="1"/>
-    <col min="10" max="10" width="8.81666666666667" style="13" customWidth="1"/>
-    <col min="11" max="11" width="32.225" style="12" customWidth="1"/>
-    <col min="12" max="12" width="10.1666666666667" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="8.94166666666667" style="12"/>
+    <col min="1" max="1" width="8.66666666666667" style="12"/>
+    <col min="2" max="2" width="25.0833333333333" style="12" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" style="12" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="12" customWidth="1"/>
+    <col min="5" max="5" width="8.66666666666667" style="12"/>
+    <col min="6" max="6" width="17" style="12" customWidth="1"/>
+    <col min="7" max="7" width="22.25" style="12" customWidth="1"/>
+    <col min="8" max="8" width="15.5" style="12" customWidth="1"/>
+    <col min="9" max="9" width="12.1666666666667" style="12" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="12" customWidth="1"/>
+    <col min="11" max="11" width="11.6666666666667" style="12" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="12" customWidth="1"/>
+    <col min="13" max="16384" width="8.66666666666667" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="14" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="14" t="s">
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="K2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="L2" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="16" t="s">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="10">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="J7" s="10">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="J8" s="10">
+        <v>3</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J9" s="10">
+        <v>4</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="B11" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="H12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="H13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="H14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="J14" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1"/>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="B16" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="17" t="s">
+      <c r="G16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="I16" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="J16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="2:10">
+      <c r="H17" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H3" s="17" t="s">
+      <c r="I17" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1"/>
+    <row r="20" customHeight="1" spans="2:10">
+      <c r="B20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="C20" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K3" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" s="17" t="s">
+      <c r="G20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="4" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="19"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="20"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-    </row>
-    <row r="5" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="I20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="19" t="b">
+      <c r="J20" s="12">
         <v>0</v>
       </c>
-      <c r="D5" s="19" t="b">
+    </row>
+    <row r="21" customHeight="1" spans="2:10">
+      <c r="H21" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="J21" s="12">
         <v>1</v>
       </c>
-      <c r="E5" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="G5" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J5" s="20">
-        <v>0</v>
-      </c>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-    </row>
-    <row r="6" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19" t="s">
+    </row>
+    <row r="22" customHeight="1" spans="2:10">
+      <c r="H22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J6" s="20">
-        <v>1</v>
-      </c>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-    </row>
-    <row r="7" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="I7" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J7" s="20">
+      <c r="J22" s="12">
         <v>2</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
-    </row>
-    <row r="8" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="J8" s="20">
-        <v>3</v>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-    </row>
-    <row r="9" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19" t="s">
-        <v>120</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="J9" s="20">
-        <v>4</v>
-      </c>
-      <c r="K9" s="19"/>
-      <c r="L9" s="19"/>
-    </row>
-    <row r="12" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="19"/>
-      <c r="B12" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D12" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>123</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J12" s="20">
-        <v>0</v>
-      </c>
-      <c r="K12" s="19"/>
-      <c r="L12" s="19"/>
-    </row>
-    <row r="13" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="19"/>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19" t="s">
-        <v>124</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>125</v>
-      </c>
-      <c r="J13" s="20">
-        <v>1</v>
-      </c>
-      <c r="K13" s="19"/>
-      <c r="L13" s="19"/>
-    </row>
-    <row r="14" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19" t="s">
-        <v>126</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>127</v>
-      </c>
-      <c r="J14" s="20">
-        <v>2</v>
-      </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="19"/>
-    </row>
-    <row r="15" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="19"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="19"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="19"/>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19" t="s">
-        <v>128</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="20">
-        <v>3</v>
-      </c>
-      <c r="K15" s="19"/>
-      <c r="L15" s="19"/>
-    </row>
-    <row r="16" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="19"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="J16" s="20">
-        <v>4</v>
-      </c>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-    </row>
-    <row r="17" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A17" s="19"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="J17" s="20">
-        <v>5</v>
-      </c>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-    </row>
-    <row r="20" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A20" s="19"/>
-      <c r="B20" s="19" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" s="20">
-        <v>0</v>
-      </c>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-    </row>
-    <row r="21" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19" t="s">
-        <v>136</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="J21" s="20">
-        <v>1</v>
-      </c>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
-      <c r="B25" s="12" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D25" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="G25" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H25" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="J25" s="20">
-        <v>0</v>
-      </c>
-      <c r="K25" s="22" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
-      <c r="F26" s="19"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I26" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="J26" s="20">
-        <v>1</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="1:12">
-      <c r="H27" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="J27" s="13">
-        <v>2</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="1:12">
-      <c r="H28" s="12" t="s">
-        <v>149</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>150</v>
-      </c>
-      <c r="J28" s="13">
-        <v>3</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="1:12">
-      <c r="B30" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D30" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="G30" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>154</v>
-      </c>
-      <c r="I30" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="J30" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="1:12">
-      <c r="H31" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="J31" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C34" s="19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" s="19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>159</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="19">
-        <v>0</v>
-      </c>
-      <c r="K34" s="19"/>
-      <c r="L34" s="19"/>
-    </row>
-    <row r="35" s="12" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A35" s="19"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19" t="s">
-        <v>160</v>
-      </c>
-      <c r="I35" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="J35" s="19">
-        <v>1</v>
-      </c>
-      <c r="K35" s="19"/>
-      <c r="L35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4026,18 +3930,618 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L35"/>
+  <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="8.94166666666667" style="1"/>
+    <col min="2" max="2" width="21.5666666666667" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.525" style="1" customWidth="1"/>
+    <col min="4" max="4" width="17.4083333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.075" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.2833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="23.0333333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.3333333333333" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.81666666666667" style="2" customWidth="1"/>
+    <col min="11" max="11" width="32.225" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.1666666666667" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.94166666666667" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="11"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J5" s="11">
+        <v>0</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="11">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="10"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="J7" s="11">
+        <v>2</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8" s="11">
+        <v>3</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="J9" s="11">
+        <v>4</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D12" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="11">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="J13" s="11">
+        <v>1</v>
+      </c>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="J14" s="11">
+        <v>2</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="J15" s="11">
+        <v>3</v>
+      </c>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="11">
+        <v>4</v>
+      </c>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="J17" s="11">
+        <v>5</v>
+      </c>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J20" s="11">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="J21" s="11">
+        <v>1</v>
+      </c>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="25" customHeight="1" spans="1:12">
+      <c r="B25" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D25" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="J25" s="11">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:12">
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="J26" s="11">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:12">
+      <c r="H27" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:12">
+      <c r="H28" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="J28" s="2">
+        <v>3</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:12">
+      <c r="B30" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:12">
+      <c r="H31" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J31" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A34" s="10"/>
+      <c r="B34" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="10" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" s="10">
+        <v>0</v>
+      </c>
+      <c r="K34" s="10"/>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A35" s="10"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="J35" s="10">
+        <v>1</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="H1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.94166666666667" style="1"/>
     <col min="2" max="2" width="22.55" style="1" customWidth="1"/>
     <col min="3" max="3" width="18.1666666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.1666666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.4083333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="10.9083333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.1583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="21.6666666666667" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7416666666667" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.0833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5833333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.6416666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.5916666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
@@ -4104,41 +4608,41 @@
       <c r="A3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="K3" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="L3" s="8" t="s">
-        <v>110</v>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="9"/>
+      <c r="F3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B5" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="C5" s="2" t="b">
         <v>0</v>
@@ -4149,17 +4653,17 @@
       <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="11" t="s">
-        <v>163</v>
+      <c r="F5" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>24</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>165</v>
+        <v>168</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -4170,10 +4674,10 @@
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
       <c r="H6" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>167</v>
+        <v>170</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="J6" s="1">
         <v>1</v>
@@ -4184,10 +4688,10 @@
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
       <c r="H7" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>169</v>
+        <v>172</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="J7" s="1">
         <v>100</v>
@@ -4198,10 +4702,10 @@
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
       <c r="H8" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="J8" s="1">
         <v>101</v>
@@ -4212,10 +4716,10 @@
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
       <c r="H9" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="J9" s="1">
         <v>102</v>
@@ -4226,10 +4730,10 @@
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
       <c r="H10" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>175</v>
+        <v>178</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="J10" s="1">
         <v>103</v>
@@ -4237,10 +4741,10 @@
     </row>
     <row r="11" customHeight="1" spans="1:12">
       <c r="H11" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>177</v>
+        <v>180</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="J11" s="1">
         <v>104</v>
@@ -4248,10 +4752,10 @@
     </row>
     <row r="12" customHeight="1" spans="1:12">
       <c r="H12" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>179</v>
+        <v>182</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="J12" s="1">
         <v>105</v>
@@ -4259,13 +4763,24 @@
     </row>
     <row r="13" customHeight="1" spans="1:12">
       <c r="H13" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>181</v>
+        <v>184</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="J13" s="1">
         <v>106</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="H14" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="1">
+        <v>107</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
   <si>
     <t>##var</t>
   </si>
@@ -1402,6 +1402,84 @@
         <charset val="134"/>
       </rPr>
       <t>局内结算面板</t>
+    </r>
+  </si>
+  <si>
+    <t>DeploymentBriefingForm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>入场简报面板</t>
+    </r>
+  </si>
+  <si>
+    <t>FadeForm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转场面板</t>
+    </r>
+  </si>
+  <si>
+    <t>LobbyPageType</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大厅界面页签类型</t>
+    </r>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>主界面</t>
+    </r>
+  </si>
+  <si>
+    <t>Warehouse</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仓库</t>
+    </r>
+  </si>
+  <si>
+    <t>Loadout</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>战备</t>
     </r>
   </si>
 </sst>
@@ -1574,12 +1652,12 @@
     </font>
     <font>
       <sz val="12"/>
+      <color rgb="FF202020"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -2086,7 +2164,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
@@ -2119,7 +2197,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
@@ -2598,7 +2675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -3149,33 +3226,33 @@
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
     </row>
-    <row r="25" s="13" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-    </row>
-    <row r="26" s="13" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
+    <row r="25" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A25" s="13"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+    </row>
+    <row r="26" s="12" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A26" s="13"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="13"/>
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+      <c r="L26" s="13"/>
     </row>
     <row r="27" customHeight="1" spans="1:12">
       <c r="A27" s="10"/>
@@ -3363,172 +3440,130 @@
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
     </row>
-    <row r="36" customHeight="1" spans="1:12">
-      <c r="A36" s="10"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-    </row>
-    <row r="37" s="13" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A37" s="14"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
+    <row r="37" customHeight="1" spans="1:12">
+      <c r="B37" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0</v>
+      </c>
+      <c r="D37" s="1">
+        <v>1</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="38" customHeight="1" spans="1:12">
-      <c r="A38" s="10"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-    </row>
-    <row r="40" customHeight="1" spans="1:12">
-      <c r="B40" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="1">
-        <v>0</v>
-      </c>
-      <c r="D40" s="1">
+      <c r="H38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="1">
         <v>1</v>
       </c>
-      <c r="E40" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="1:12">
-      <c r="H41" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="1:12">
-      <c r="H42" s="1" t="s">
+    </row>
+    <row r="39" customHeight="1" spans="1:12">
+      <c r="H39" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="J42" s="1">
+      <c r="J39" s="1">
         <v>2</v>
       </c>
     </row>
+    <row r="42" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+    </row>
     <row r="45" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
     </row>
     <row r="46" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A46" s="15"/>
-      <c r="B46" s="15"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A47" s="15"/>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A48" s="15"/>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15"/>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
-      <c r="G48" s="15"/>
-      <c r="H48" s="15"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15"/>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="15"/>
-      <c r="H49" s="15"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1"/>
-    <row r="52" customFormat="1" customHeight="1"/>
-    <row r="53" customFormat="1" customHeight="1"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1"/>
+    <row r="49" customFormat="1" customHeight="1"/>
+    <row r="50" customFormat="1" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
@@ -3544,19 +3579,19 @@
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="8.66666666666667" style="12"/>
-    <col min="2" max="2" width="25.0833333333333" style="12" customWidth="1"/>
-    <col min="3" max="3" width="18.6666666666667" style="12" customWidth="1"/>
-    <col min="4" max="4" width="16.75" style="12" customWidth="1"/>
-    <col min="5" max="5" width="8.66666666666667" style="12"/>
-    <col min="6" max="6" width="17" style="12" customWidth="1"/>
-    <col min="7" max="7" width="22.25" style="12" customWidth="1"/>
-    <col min="8" max="8" width="15.5" style="12" customWidth="1"/>
-    <col min="9" max="9" width="12.1666666666667" style="12" customWidth="1"/>
-    <col min="10" max="10" width="11.75" style="12" customWidth="1"/>
-    <col min="11" max="11" width="11.6666666666667" style="12" customWidth="1"/>
-    <col min="12" max="12" width="12.75" style="12" customWidth="1"/>
-    <col min="13" max="16384" width="8.66666666666667" style="12"/>
+    <col min="1" max="1" width="8.66666666666667" style="1"/>
+    <col min="2" max="2" width="25.0833333333333" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8.66666666666667" style="1"/>
+    <col min="6" max="6" width="18.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="22.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6666666666667" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.66666666666667" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
@@ -3825,7 +3860,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1"/>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="B16" s="1" t="s">
         <v>102</v>
@@ -3866,7 +3900,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" s="1" customFormat="1" customHeight="1"/>
     <row r="20" customHeight="1" spans="2:10">
       <c r="B20" s="1" t="s">
         <v>108</v>
@@ -3892,7 +3925,7 @@
       <c r="I20" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="1">
         <v>0</v>
       </c>
     </row>
@@ -3903,7 +3936,7 @@
       <c r="I21" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="1">
         <v>1</v>
       </c>
     </row>
@@ -3914,7 +3947,7 @@
       <c r="I22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="1">
         <v>2</v>
       </c>
     </row>
@@ -4530,7 +4563,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.94166666666667" style="1"/>
@@ -4538,9 +4571,9 @@
     <col min="3" max="3" width="18.1666666666667" style="2" customWidth="1"/>
     <col min="4" max="4" width="17.1666666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="10.4083333333333" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.9083333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="18.4166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.1583333333333" style="1" customWidth="1"/>
-    <col min="8" max="8" width="25.0833333333333" style="1" customWidth="1"/>
+    <col min="8" max="8" width="26.0833333333333" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.5833333333333" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.6416666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.5916666666667" style="1" customWidth="1"/>
@@ -4673,6 +4706,8 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="3"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
         <v>170</v>
       </c>
@@ -4687,6 +4722,8 @@
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="3"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
         <v>172</v>
       </c>
@@ -4701,6 +4738,8 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="3"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
       <c r="H8" s="1" t="s">
         <v>174</v>
       </c>
@@ -4715,6 +4754,8 @@
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="3"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
       <c r="H9" s="1" t="s">
         <v>176</v>
       </c>
@@ -4729,6 +4770,8 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="3"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
       <c r="H10" s="1" t="s">
         <v>178</v>
       </c>
@@ -4781,6 +4824,79 @@
       </c>
       <c r="J14" s="1">
         <v>107</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="H15" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J15" s="1">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="H16" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J16" s="1">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="2:10">
+      <c r="B18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="C18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:10">
+      <c r="H19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:10">
+      <c r="H20" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J20" s="1">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/__enums__.xlsx
+++ b/数据表/Datas/__enums__.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="202">
   <si>
     <t>##var</t>
   </si>
@@ -1428,6 +1428,19 @@
         <charset val="134"/>
       </rPr>
       <t>转场面板</t>
+    </r>
+  </si>
+  <si>
+    <t>ItemDragOverlayForm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>拖拽道具时顶层面板</t>
     </r>
   </si>
   <si>
@@ -4563,7 +4576,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.94166666666667" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="8.94166666666667" style="1"/>
@@ -4574,7 +4587,7 @@
     <col min="6" max="6" width="18.4166666666667" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.1583333333333" style="1" customWidth="1"/>
     <col min="8" max="8" width="26.0833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="1" customWidth="1"/>
     <col min="10" max="10" width="11.6416666666667" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.5916666666667" style="1" customWidth="1"/>
     <col min="12" max="12" width="13.5" style="1" customWidth="1"/>
@@ -4848,36 +4861,36 @@
         <v>109</v>
       </c>
     </row>
-    <row r="18" customHeight="1" spans="2:10">
-      <c r="B18" s="1" t="s">
+    <row r="17" customHeight="1" spans="2:10">
+      <c r="H17" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C18" s="2" t="b">
+      <c r="I17" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="J17" s="1">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:10">
+      <c r="B19" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="D18" s="2" t="b">
+      <c r="D19" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="1" t="s">
+      <c r="F19" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="2:10">
       <c r="H19" s="1" t="s">
         <v>196</v>
       </c>
@@ -4885,7 +4898,7 @@
         <v>197</v>
       </c>
       <c r="J19" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="2:10">
@@ -4896,6 +4909,17 @@
         <v>199</v>
       </c>
       <c r="J20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:10">
+      <c r="H21" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="J21" s="1">
         <v>2</v>
       </c>
     </row>
